--- a/planering/kemi-omrade2/kemi-2-kahoot.xlsx
+++ b/planering/kemi-omrade2/kemi-2-kahoot.xlsx
@@ -1880,17 +1880,17 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
+          <t>Bara fasta föremål</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Bara det som väger mer än 1 kg</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
           <t>Allt som går att se</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>Bara fasta föremål</t>
-        </is>
-      </c>
-      <c r="F9" s="14" t="inlineStr">
-        <is>
-          <t>Bara det som väger mer än 1 kg</t>
         </is>
       </c>
       <c r="G9" s="14" t="n">
@@ -1932,22 +1932,22 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
+          <t>Långt ifrån varandra</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>Tätt i ett mönster och de vibrerar</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>De står helt stilla</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
           <t>De glider fritt förbi varandra</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>Tätt i ett mönster och de vibrerar</t>
-        </is>
-      </c>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>Långt ifrån varandra</t>
-        </is>
-      </c>
-      <c r="F10" s="14" t="inlineStr">
-        <is>
-          <t>De står helt stilla</t>
         </is>
       </c>
       <c r="G10" s="14" t="n">
@@ -1989,12 +1989,12 @@
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
+          <t>De glider förbi varandra tätt</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
           <t>De rör sig inte alls</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t>De glider förbi varandra tätt</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
+          <t>Att vatten är blött</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>Att is är hård</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
           <t>Att metall leder värme</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>Att is är hård</t>
-        </is>
-      </c>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>Att vatten är blött</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
@@ -2108,17 +2108,17 @@
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
+          <t>Massa gånger volym</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>Volym delat med massa</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
           <t>Massa plus volym</t>
-        </is>
-      </c>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>Volym delat med massa</t>
-        </is>
-      </c>
-      <c r="F13" s="14" t="inlineStr">
-        <is>
-          <t>Massa gånger volym</t>
         </is>
       </c>
       <c r="G13" s="14" t="n">
@@ -2160,22 +2160,22 @@
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
+          <t>32 g/cm³</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>3 g/cm³</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>16 g/cm³</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
           <t>0,33 g/cm³</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>3 g/cm³</t>
-        </is>
-      </c>
-      <c r="E14" s="14" t="inlineStr">
-        <is>
-          <t>16 g/cm³</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="inlineStr">
-        <is>
-          <t>32 g/cm³</t>
         </is>
       </c>
       <c r="G14" s="14" t="n">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
+          <t>Is är kallare</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
           <t>Is har ingen massa</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="inlineStr">
-        <is>
-          <t>Is är kallare</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
@@ -2274,17 +2274,17 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
+          <t>Med en termometer</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>Med ett filter</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
           <t>Med en våg</t>
-        </is>
-      </c>
-      <c r="D16" s="14" t="inlineStr">
-        <is>
-          <t>Med en termometer</t>
-        </is>
-      </c>
-      <c r="E16" s="14" t="inlineStr">
-        <is>
-          <t>Med ett filter</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -2336,17 +2336,17 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
+          <t>Stelning</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
           <t>Förångning</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>Kondensation</t>
-        </is>
-      </c>
-      <c r="F17" s="14" t="inlineStr">
-        <is>
-          <t>Stelning</t>
         </is>
       </c>
       <c r="G17" s="14" t="n">
@@ -2398,12 +2398,12 @@
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
+          <t>Smältning</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
           <t>Stelning</t>
-        </is>
-      </c>
-      <c r="F18" s="14" t="inlineStr">
-        <is>
-          <t>Smältning</t>
         </is>
       </c>
       <c r="G18" s="14" t="n">
@@ -2445,22 +2445,22 @@
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
+          <t>Vattnet är redan 100 °C</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>Termometern slutar fungera</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>Värmen går åt att bryta loss partiklarna</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
           <t>Isen tar inte emot värme</t>
-        </is>
-      </c>
-      <c r="D19" s="14" t="inlineStr">
-        <is>
-          <t>Termometern slutar fungera</t>
-        </is>
-      </c>
-      <c r="E19" s="14" t="inlineStr">
-        <is>
-          <t>Värmen går åt att bryta loss partiklarna</t>
-        </is>
-      </c>
-      <c r="F19" s="14" t="inlineStr">
-        <is>
-          <t>Vattnet är redan 100 °C</t>
         </is>
       </c>
       <c r="G19" s="14" t="n">
@@ -2564,17 +2564,17 @@
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
+          <t>Sand i vatten</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>Sallad</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
+        <is>
           <t>Granit</t>
-        </is>
-      </c>
-      <c r="E21" s="14" t="inlineStr">
-        <is>
-          <t>Sand i vatten</t>
-        </is>
-      </c>
-      <c r="F21" s="14" t="inlineStr">
-        <is>
-          <t>Sallad</t>
         </is>
       </c>
       <c r="G21" s="14" t="n">
@@ -2616,22 +2616,22 @@
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
+          <t>Destillat</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>Lösningsmedel</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
           <t>Fällning</t>
         </is>
       </c>
-      <c r="D22" s="14" t="inlineStr">
-        <is>
-          <t>Lösningsmedel</t>
-        </is>
-      </c>
-      <c r="E22" s="14" t="inlineStr">
+      <c r="F22" s="14" t="inlineStr">
         <is>
           <t>Filtrat</t>
-        </is>
-      </c>
-      <c r="F22" s="14" t="inlineStr">
-        <is>
-          <t>Destillat</t>
         </is>
       </c>
       <c r="G22" s="14" t="n">
@@ -2678,17 +2678,17 @@
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
+          <t>Diffusion</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>Filtrering</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
           <t>Fällning</t>
-        </is>
-      </c>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>Filtrering</t>
-        </is>
-      </c>
-      <c r="F23" s="14" t="inlineStr">
-        <is>
-          <t>Diffusion</t>
         </is>
       </c>
       <c r="G23" s="14" t="n">
@@ -2730,17 +2730,17 @@
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
+          <t>Rör om länge</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>Frys blandningen</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
           <t>Filtrera blandningen</t>
-        </is>
-      </c>
-      <c r="D24" s="14" t="inlineStr">
-        <is>
-          <t>Frys blandningen</t>
-        </is>
-      </c>
-      <c r="E24" s="14" t="inlineStr">
-        <is>
-          <t>Rör om länge</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
@@ -2844,22 +2844,22 @@
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
+          <t>Att ämnen har olika färg</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Att ämnen har olika kokpunkter</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>Att ämnen har olika massa</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
           <t>Att ämnen har olika form</t>
-        </is>
-      </c>
-      <c r="D26" s="14" t="inlineStr">
-        <is>
-          <t>Att ämnen har olika kokpunkter</t>
-        </is>
-      </c>
-      <c r="E26" s="14" t="inlineStr">
-        <is>
-          <t>Att ämnen har olika färg</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="inlineStr">
-        <is>
-          <t>Att ämnen har olika massa</t>
         </is>
       </c>
       <c r="G26" s="14" t="n">
@@ -2901,22 +2901,22 @@
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
+          <t>Att filtrera sand</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>Att mäta densitet</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>Att skilja ämnen som vandrar olika långt</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
           <t>Att kyla vätskor</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>Att mäta densitet</t>
-        </is>
-      </c>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>Att skilja ämnen som vandrar olika långt</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>Att filtrera sand</t>
         </is>
       </c>
       <c r="G27" s="14" t="n">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
+          <t>En gas som bildas vid kokning</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>Ett filter av papper</t>
+        </is>
+      </c>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
           <t>En sorts lösningsmedel</t>
-        </is>
-      </c>
-      <c r="D28" s="14" t="inlineStr">
-        <is>
-          <t>Ett filter av papper</t>
-        </is>
-      </c>
-      <c r="E28" s="14" t="inlineStr">
-        <is>
-          <t>En gas som bildas vid kokning</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
@@ -3020,17 +3020,17 @@
       </c>
       <c r="D29" s="16" t="inlineStr">
         <is>
+          <t>119 %</t>
+        </is>
+      </c>
+      <c r="E29" s="16" t="inlineStr">
+        <is>
+          <t>4,2 %</t>
+        </is>
+      </c>
+      <c r="F29" s="16" t="inlineStr">
+        <is>
           <t>16 %</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>4,2 %</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>119 %</t>
         </is>
       </c>
       <c r="G29" s="14" t="n">
@@ -3072,17 +3072,17 @@
       </c>
       <c r="C30" s="16" t="inlineStr">
         <is>
+          <t>Det räcker alltid med smältpunkt</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="inlineStr">
+        <is>
+          <t>Flera ämnen kan ha liknande värde på en egenskap</t>
+        </is>
+      </c>
+      <c r="E30" s="16" t="inlineStr">
+        <is>
           <t>Alla ämnen har samma egenskaper</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>Flera ämnen kan ha liknande värde på en egenskap</t>
-        </is>
-      </c>
-      <c r="E30" s="16" t="inlineStr">
-        <is>
-          <t>Det räcker alltid med smältpunkt</t>
         </is>
       </c>
       <c r="F30" s="16" t="inlineStr">
